--- a/Assets/Data/Excel/CharacterData.xlsx
+++ b/Assets/Data/Excel/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4007FE60-1144-47B9-A304-EE57C3BF9480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1760F4-0087-41FF-9C24-B3C947286C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="5145" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Data/Excel/CharacterData.xlsx
+++ b/Assets/Data/Excel/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1760F4-0087-41FF-9C24-B3C947286C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8036A82-3384-4B29-975B-022C75443666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="4200" windowWidth="13380" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,6 +108,37 @@
   <si>
     <t>100|100|5|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全能者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150|150|10|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102|102|13|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gladiator_icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well_rounded_icon</t>
   </si>
 </sst>
 </file>
@@ -551,12 +582,24 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="A5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -565,12 +608,24 @@
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="A6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>

--- a/Assets/Data/Excel/CharacterData.xlsx
+++ b/Assets/Data/Excel/CharacterData.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8036A82-3384-4B29-975B-022C75443666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850582D8-2F49-4202-B5C7-520E94F7B495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="4200" windowWidth="13380" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6660" yWindow="6075" windowWidth="13380" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,117 +25,107 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>characterName</t>
+  </si>
+  <si>
+    <t>characterImage</t>
+  </si>
+  <si>
+    <t>attrIds</t>
+  </si>
+  <si>
+    <t>attrData</t>
+  </si>
+  <si>
+    <t>startingWeaponIds</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>提供给外部使用的角色的ID编号</t>
+  </si>
+  <si>
+    <t>他的职业是什么</t>
+  </si>
+  <si>
+    <t>角色的名字</t>
+  </si>
+  <si>
+    <t>资源在Resource里面的名字，后面改成对应的路径</t>
+  </si>
+  <si>
+    <t>角色有的属性</t>
+  </si>
+  <si>
+    <t>角色对应属性的基础值</t>
+  </si>
+  <si>
+    <t>角色可选起始武器ID列表</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>回声</t>
+  </si>
+  <si>
+    <t>echo</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9|10|11|12|13|14|15|16|17|18|19</t>
+  </si>
+  <si>
+    <t>全能</t>
+  </si>
+  <si>
+    <t>全能者</t>
+  </si>
+  <si>
+    <t>well_rounded_icon</t>
+  </si>
+  <si>
+    <t>150|150|10|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
+  </si>
+  <si>
+    <t>201|202|203</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>Gladiator_icon</t>
+  </si>
+  <si>
+    <t>102|102|13|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
+  </si>
+  <si>
+    <t>202|203</t>
+  </si>
+  <si>
+    <t>100|100|5|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|1000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>job</t>
+    <t>201|203|205</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>characterName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>characterImage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>echo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回声</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attrIds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attrData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供给外部使用的角色的ID编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>他的职业是什么</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>射手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色的名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资源在Resource里面的名字，后面改成对应的路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色有的属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色对应属性的基础值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1|2|3|4|5|6|7|8|9|10|11|12|13|14|15|16|17|18|19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100|100|5|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全能者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狂战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>150|150|10|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>102|102|13|10|5|5|5|2|5|10|0|5|10|5|10|10|10|0|0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gladiator_icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>well_rounded_icon</t>
   </si>
 </sst>
 </file>
@@ -491,12 +478,14 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -505,24 +494,26 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -531,24 +522,26 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -560,21 +553,23 @@
         <v>1001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -586,21 +581,23 @@
         <v>1002</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -612,21 +609,23 @@
         <v>1003</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
